--- a/RFO_Stakeholders Final.xlsx
+++ b/RFO_Stakeholders Final.xlsx
@@ -8,26 +8,27 @@
   <sheets>
     <sheet name="RFO_Stakeholders Final" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="5Ws MODEL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="4Ws MODEL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="5Ws Guide" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5Ws Database" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="RFO STAKEHOLDER HISTORY" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Coverage Summary" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Data Notes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Data Sources" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Historical Coverage" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="3W Matrix (Who does What Where)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Cluster Summary (Who Does What)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="WorldPop Estimates" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4Ws MODEL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5Ws Guide" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5Ws Database" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="RFO STAKEHOLDER HISTORY" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Coverage Summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data Notes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Data Sources" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Historical Coverage" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="3W Matrix (Who does What Where)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Cluster Summary (Who Does What)" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RFO_Stakeholders Final'!$A$1:$T$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'5Ws MODEL'!$A$1:$X$154</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'4Ws MODEL'!$A$1:$W$154</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5Ws Database'!$A$1:$V$154</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'RFO STAKEHOLDER HISTORY'!$A$1:$I$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage Summary'!$A$1:$G$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Data Sources'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Historical Coverage'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4Ws MODEL'!$A$1:$W$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'5Ws Database'!$A$1:$V$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'RFO STAKEHOLDER HISTORY'!$A$1:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Coverage Summary'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Data Sources'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Historical Coverage'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -4275,6 +4276,189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Publisher</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Coverage / use</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Publication / extract date</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Use in workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>République Démocratique du Congo : Présence Opérationnelle</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>OCHA Democratic Republic of the Congo / HDX</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>Operational presence (projects, dates, territory, province, actor and cluster); Admin 3 registry</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Extract February 2026; dataset range 2022-2026</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>Verified Mambasa records and operation dates</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>DRC - 3 W National - Mai 2018</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>OCHA Democratic Republic of the Congo / HDX</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Historical 3W project compilation</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>2018-06-28</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>https://data.humdata.org/dataset/drc-3-w-national-mai-2018</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Background reference only; not used to assert current presence</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>DRC Displacement Data - Ituri Province - Baseline Assessment</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>IOM DTM / HDX</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Displacement and needs data, including Mambasa territory</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Current cycle July 2026</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>https://data.humdata.org/dataset/drc-displacement-data-ituri-province-baseline-assessment-iom-dtm</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Contextual reference; not an organisation-operations source</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WorldPop DRC Population 2024 R2025A v1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>WorldPop, University of Southampton</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>100 m constrained population raster; used for 5 km locality-denominator estimates and 10% intervention planning scenarios</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2024 population year; product dated 2025-09-01</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://hub.worldpop.org/geodata/summary?id=73054</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>WorldPop locality population and scenario beneficiary estimates</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4449,7 +4633,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7513,7 +7697,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7715,7 +7899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X154"/>
+  <dimension ref="A1:AD154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7740,9 +7924,15 @@
     <col width="55" customWidth="1" min="20" max="20"/>
     <col width="24" customWidth="1" min="21" max="21"/>
     <col width="75" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="28" customWidth="1" min="26" max="26"/>
+    <col width="75" customWidth="1" min="27" max="27"/>
+    <col width="85" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
-    <row r="1" ht="58" customHeight="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
           <t>5Ws ID</t>
@@ -7861,6 +8051,36 @@
       <c r="X1" s="13" t="inlineStr">
         <is>
           <t>Population Source</t>
+        </is>
+      </c>
+      <c r="Y1" s="13" t="inlineStr">
+        <is>
+          <t>WorldPop Locality Population (2024)</t>
+        </is>
+      </c>
+      <c r="Z1" s="13" t="inlineStr">
+        <is>
+          <t>Estimation Radius (km)</t>
+        </is>
+      </c>
+      <c r="AA1" s="13" t="inlineStr">
+        <is>
+          <t>Planning Coverage Factor</t>
+        </is>
+      </c>
+      <c r="AB1" s="13" t="inlineStr">
+        <is>
+          <t>Estimated Beneficiaries / Intervention</t>
+        </is>
+      </c>
+      <c r="AC1" s="13" t="inlineStr">
+        <is>
+          <t>Beneficiary Estimate QA</t>
+        </is>
+      </c>
+      <c r="AD1" s="13" t="inlineStr">
+        <is>
+          <t>WorldPop Source</t>
         </is>
       </c>
     </row>
@@ -7963,12 +8183,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W2" s="9" t="n">
+      <c r="W2" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X2" s="9" t="inlineStr">
+      <c r="X2" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y2" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z2" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA2" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD2" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -8071,12 +8313,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W3" s="9" t="n">
+      <c r="W3" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X3" s="9" t="inlineStr">
+      <c r="X3" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y3" s="5" t="n">
+        <v>669</v>
+      </c>
+      <c r="Z3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA3" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB3" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="AC3" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD3" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -8179,12 +8443,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X4" s="9" t="inlineStr">
+      <c r="X4" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y4" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA4" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB4" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC4" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD4" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -8287,12 +8573,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X5" s="9" t="inlineStr">
+      <c r="X5" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y5" s="5" t="n">
+        <v>106896</v>
+      </c>
+      <c r="Z5" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA5" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB5" s="5" t="n">
+        <v>10690</v>
+      </c>
+      <c r="AC5" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD5" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -8395,12 +8703,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X6" s="9" t="inlineStr">
+      <c r="X6" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y6" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA6" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD6" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -8503,12 +8833,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X7" s="9" t="inlineStr">
+      <c r="X7" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y7" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA7" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD7" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -8611,12 +8963,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X8" s="9" t="inlineStr">
+      <c r="X8" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y8" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA8" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD8" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -8719,12 +9093,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W9" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X9" s="9" t="inlineStr">
+      <c r="X9" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y9" s="5" t="n">
+        <v>669</v>
+      </c>
+      <c r="Z9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB9" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="AC9" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD9" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -8827,12 +9223,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X10" s="9" t="inlineStr">
+      <c r="X10" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y10" s="5" t="n">
+        <v>669</v>
+      </c>
+      <c r="Z10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB10" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="AC10" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD10" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -8935,12 +9353,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X11" s="9" t="inlineStr">
+      <c r="X11" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y11" s="5" t="n">
+        <v>669</v>
+      </c>
+      <c r="Z11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA11" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB11" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="AC11" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD11" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -9043,12 +9483,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W12" s="9" t="n">
+      <c r="W12" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X12" s="9" t="inlineStr">
+      <c r="X12" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z12" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA12" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD12" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9613,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X13" s="9" t="inlineStr">
+      <c r="X13" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z13" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA13" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD13" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -9259,12 +9743,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W14" s="9" t="n">
+      <c r="W14" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X14" s="9" t="inlineStr">
+      <c r="X14" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y14" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA14" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD14" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -9367,12 +9873,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X15" s="9" t="inlineStr">
+      <c r="X15" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y15" s="5" t="n">
+        <v>669</v>
+      </c>
+      <c r="Z15" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA15" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB15" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="AC15" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD15" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -9475,12 +10003,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W16" s="9" t="n">
+      <c r="W16" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X16" s="9" t="inlineStr">
+      <c r="X16" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y16" s="5" t="n">
+        <v>669</v>
+      </c>
+      <c r="Z16" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA16" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB16" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="AC16" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD16" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -9583,12 +10133,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X17" s="9" t="inlineStr">
+      <c r="X17" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y17" s="5" t="n">
+        <v>669</v>
+      </c>
+      <c r="Z17" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB17" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="AC17" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD17" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -9691,12 +10263,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X18" s="9" t="inlineStr">
+      <c r="X18" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y18" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z18" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA18" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB18" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC18" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD18" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -9799,12 +10393,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X19" s="9" t="inlineStr">
+      <c r="X19" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y19" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z19" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA19" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC19" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD19" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -9907,12 +10523,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W20" s="9" t="n">
+      <c r="W20" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X20" s="9" t="inlineStr">
+      <c r="X20" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y20" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA20" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB20" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC20" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD20" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -10015,12 +10653,38 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W21" s="9" t="n">
+      <c r="W21" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X21" s="9" t="inlineStr">
+      <c r="X21" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y21" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Z21" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA21" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB21" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AC21" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD21" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10787,38 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X22" s="9" t="inlineStr">
+      <c r="X22" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y22" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Z22" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB22" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="AC22" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD22" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -10231,12 +10921,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X23" s="9" t="inlineStr">
+      <c r="X23" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y23" s="5" t="n">
+        <v>106896</v>
+      </c>
+      <c r="Z23" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA23" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB23" s="5" t="n">
+        <v>10690</v>
+      </c>
+      <c r="AC23" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD23" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -10339,12 +11051,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X24" s="9" t="inlineStr">
+      <c r="X24" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y24" s="5" t="n">
+        <v>106896</v>
+      </c>
+      <c r="Z24" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA24" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB24" s="5" t="n">
+        <v>10690</v>
+      </c>
+      <c r="AC24" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD24" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -10447,12 +11181,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W25" s="9" t="n">
+      <c r="W25" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X25" s="9" t="inlineStr">
+      <c r="X25" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y25" s="5" t="n">
+        <v>236</v>
+      </c>
+      <c r="Z25" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA25" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB25" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC25" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD25" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -10555,12 +11311,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W26" s="9" t="n">
+      <c r="W26" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X26" s="9" t="inlineStr">
+      <c r="X26" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y26" s="5" t="n">
+        <v>236</v>
+      </c>
+      <c r="Z26" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA26" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB26" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC26" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD26" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -10663,12 +11441,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W27" s="9" t="n">
+      <c r="W27" s="5" t="n">
         <v>561587</v>
       </c>
-      <c r="X27" s="9" t="inlineStr">
+      <c r="X27" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y27" s="5" t="n">
+        <v>52598</v>
+      </c>
+      <c r="Z27" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA27" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB27" s="5" t="n">
+        <v>5260</v>
+      </c>
+      <c r="AC27" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD27" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -10771,12 +11571,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="5" t="n">
         <v>561587</v>
       </c>
-      <c r="X28" s="9" t="inlineStr">
+      <c r="X28" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y28" s="5" t="n">
+        <v>52598</v>
+      </c>
+      <c r="Z28" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA28" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB28" s="5" t="n">
+        <v>5260</v>
+      </c>
+      <c r="AC28" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD28" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -10879,12 +11701,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W29" s="9" t="n">
+      <c r="W29" s="5" t="n">
         <v>561587</v>
       </c>
-      <c r="X29" s="9" t="inlineStr">
+      <c r="X29" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y29" s="5" t="n">
+        <v>52598</v>
+      </c>
+      <c r="Z29" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB29" s="5" t="n">
+        <v>5260</v>
+      </c>
+      <c r="AC29" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD29" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -10987,12 +11831,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W30" s="9" t="n">
+      <c r="W30" s="5" t="n">
         <v>561587</v>
       </c>
-      <c r="X30" s="9" t="inlineStr">
+      <c r="X30" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y30" s="5" t="n">
+        <v>52598</v>
+      </c>
+      <c r="Z30" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA30" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB30" s="5" t="n">
+        <v>5260</v>
+      </c>
+      <c r="AC30" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD30" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -11095,12 +11961,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="5" t="n">
         <v>561587</v>
       </c>
-      <c r="X31" s="9" t="inlineStr">
+      <c r="X31" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y31" s="5" t="n">
+        <v>13082</v>
+      </c>
+      <c r="Z31" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA31" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB31" s="5" t="n">
+        <v>1308</v>
+      </c>
+      <c r="AC31" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD31" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -11203,12 +12091,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W32" s="9" t="n">
+      <c r="W32" s="5" t="n">
         <v>561587</v>
       </c>
-      <c r="X32" s="9" t="inlineStr">
+      <c r="X32" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y32" s="5" t="n">
+        <v>13082</v>
+      </c>
+      <c r="Z32" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA32" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB32" s="5" t="n">
+        <v>1308</v>
+      </c>
+      <c r="AC32" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD32" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -11311,12 +12221,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="5" t="n">
         <v>561587</v>
       </c>
-      <c r="X33" s="9" t="inlineStr">
+      <c r="X33" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y33" s="5" t="n">
+        <v>13082</v>
+      </c>
+      <c r="Z33" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA33" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB33" s="5" t="n">
+        <v>1308</v>
+      </c>
+      <c r="AC33" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD33" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -11419,12 +12351,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W34" s="9" t="n">
+      <c r="W34" s="5" t="n">
         <v>561587</v>
       </c>
-      <c r="X34" s="9" t="inlineStr">
+      <c r="X34" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y34" s="5" t="n">
+        <v>13082</v>
+      </c>
+      <c r="Z34" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA34" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB34" s="5" t="n">
+        <v>1308</v>
+      </c>
+      <c r="AC34" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD34" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -11527,12 +12481,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W35" s="9" t="n">
+      <c r="W35" s="5" t="n">
         <v>561587</v>
       </c>
-      <c r="X35" s="9" t="inlineStr">
+      <c r="X35" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y35" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z35" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA35" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC35" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD35" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -11635,12 +12611,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W36" s="9" t="n">
+      <c r="W36" s="5" t="n">
         <v>561587</v>
       </c>
-      <c r="X36" s="9" t="inlineStr">
+      <c r="X36" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y36" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z36" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA36" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB36" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC36" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD36" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -11743,12 +12741,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W37" s="9" t="n">
+      <c r="W37" s="5" t="n">
         <v>561587</v>
       </c>
-      <c r="X37" s="9" t="inlineStr">
+      <c r="X37" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y37" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z37" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA37" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC37" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD37" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -11851,12 +12871,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="5" t="n">
         <v>561587</v>
       </c>
-      <c r="X38" s="9" t="inlineStr">
+      <c r="X38" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y38" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z38" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA38" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB38" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC38" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD38" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -11959,12 +13001,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W39" s="9" t="n">
+      <c r="W39" s="5" t="n">
         <v>561587</v>
       </c>
-      <c r="X39" s="9" t="inlineStr">
+      <c r="X39" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y39" s="5" t="n">
+        <v>52598</v>
+      </c>
+      <c r="Z39" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA39" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB39" s="5" t="n">
+        <v>5260</v>
+      </c>
+      <c r="AC39" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD39" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -12067,12 +13131,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W40" s="9" t="n">
+      <c r="W40" s="5" t="n">
         <v>385896</v>
       </c>
-      <c r="X40" s="9" t="inlineStr">
+      <c r="X40" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y40" s="5" t="n">
+        <v>75747</v>
+      </c>
+      <c r="Z40" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA40" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB40" s="5" t="n">
+        <v>7575</v>
+      </c>
+      <c r="AC40" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD40" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -12175,12 +13261,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W41" s="9" t="n">
+      <c r="W41" s="5" t="n">
         <v>385896</v>
       </c>
-      <c r="X41" s="9" t="inlineStr">
+      <c r="X41" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y41" s="5" t="n">
+        <v>75747</v>
+      </c>
+      <c r="Z41" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA41" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB41" s="5" t="n">
+        <v>7575</v>
+      </c>
+      <c r="AC41" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD41" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -12283,12 +13391,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W42" s="9" t="n">
+      <c r="W42" s="5" t="n">
         <v>385896</v>
       </c>
-      <c r="X42" s="9" t="inlineStr">
+      <c r="X42" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y42" s="5" t="n">
+        <v>75747</v>
+      </c>
+      <c r="Z42" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA42" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB42" s="5" t="n">
+        <v>7575</v>
+      </c>
+      <c r="AC42" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD42" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -12391,12 +13521,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W43" s="9" t="n">
+      <c r="W43" s="5" t="n">
         <v>385896</v>
       </c>
-      <c r="X43" s="9" t="inlineStr">
+      <c r="X43" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y43" s="5" t="n">
+        <v>75747</v>
+      </c>
+      <c r="Z43" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA43" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB43" s="5" t="n">
+        <v>7575</v>
+      </c>
+      <c r="AC43" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD43" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -12499,12 +13651,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W44" s="9" t="n">
+      <c r="W44" s="5" t="n">
         <v>385896</v>
       </c>
-      <c r="X44" s="9" t="inlineStr">
+      <c r="X44" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y44" s="5" t="n">
+        <v>75747</v>
+      </c>
+      <c r="Z44" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA44" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB44" s="5" t="n">
+        <v>7575</v>
+      </c>
+      <c r="AC44" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD44" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -12607,12 +13781,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W45" s="9" t="n">
+      <c r="W45" s="5" t="n">
         <v>385896</v>
       </c>
-      <c r="X45" s="9" t="inlineStr">
+      <c r="X45" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y45" s="5" t="n">
+        <v>73911</v>
+      </c>
+      <c r="Z45" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA45" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB45" s="5" t="n">
+        <v>7391</v>
+      </c>
+      <c r="AC45" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD45" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -12715,12 +13911,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W46" s="9" t="n">
+      <c r="W46" s="5" t="n">
         <v>385896</v>
       </c>
-      <c r="X46" s="9" t="inlineStr">
+      <c r="X46" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y46" s="5" t="n">
+        <v>73911</v>
+      </c>
+      <c r="Z46" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA46" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB46" s="5" t="n">
+        <v>7391</v>
+      </c>
+      <c r="AC46" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD46" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -12823,12 +14041,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W47" s="9" t="n">
+      <c r="W47" s="5" t="n">
         <v>385896</v>
       </c>
-      <c r="X47" s="9" t="inlineStr">
+      <c r="X47" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y47" s="5" t="n">
+        <v>73911</v>
+      </c>
+      <c r="Z47" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA47" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB47" s="5" t="n">
+        <v>7391</v>
+      </c>
+      <c r="AC47" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD47" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -12931,12 +14171,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W48" s="9" t="n">
+      <c r="W48" s="5" t="n">
         <v>385896</v>
       </c>
-      <c r="X48" s="9" t="inlineStr">
+      <c r="X48" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y48" s="5" t="n">
+        <v>73911</v>
+      </c>
+      <c r="Z48" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB48" s="5" t="n">
+        <v>7391</v>
+      </c>
+      <c r="AC48" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD48" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -13039,12 +14301,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W49" s="9" t="n">
+      <c r="W49" s="5" t="n">
         <v>385896</v>
       </c>
-      <c r="X49" s="9" t="inlineStr">
+      <c r="X49" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y49" s="5" t="n">
+        <v>73911</v>
+      </c>
+      <c r="Z49" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA49" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB49" s="5" t="n">
+        <v>7391</v>
+      </c>
+      <c r="AC49" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD49" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -13147,12 +14431,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W50" s="9" t="n">
+      <c r="W50" s="5" t="n">
         <v>385896</v>
       </c>
-      <c r="X50" s="9" t="inlineStr">
+      <c r="X50" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y50" s="5" t="n">
+        <v>2103</v>
+      </c>
+      <c r="Z50" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA50" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB50" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="AC50" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD50" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -13255,12 +14561,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W51" s="9" t="n">
+      <c r="W51" s="5" t="n">
         <v>385896</v>
       </c>
-      <c r="X51" s="9" t="inlineStr">
+      <c r="X51" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y51" s="5" t="n">
+        <v>2103</v>
+      </c>
+      <c r="Z51" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA51" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB51" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="AC51" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD51" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -13363,12 +14691,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W52" s="9" t="n">
+      <c r="W52" s="5" t="n">
         <v>385896</v>
       </c>
-      <c r="X52" s="9" t="inlineStr">
+      <c r="X52" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y52" s="5" t="n">
+        <v>2103</v>
+      </c>
+      <c r="Z52" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA52" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB52" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="AC52" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD52" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -13471,12 +14821,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W53" s="9" t="n">
+      <c r="W53" s="5" t="n">
         <v>385896</v>
       </c>
-      <c r="X53" s="9" t="inlineStr">
+      <c r="X53" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y53" s="5" t="n">
+        <v>2103</v>
+      </c>
+      <c r="Z53" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA53" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB53" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="AC53" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD53" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -13579,12 +14951,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W54" s="9" t="n">
+      <c r="W54" s="5" t="n">
         <v>385896</v>
       </c>
-      <c r="X54" s="9" t="inlineStr">
+      <c r="X54" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y54" s="5" t="n">
+        <v>2103</v>
+      </c>
+      <c r="Z54" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA54" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB54" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="AC54" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD54" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -13687,12 +15081,34 @@
           <t>Internal source workbook; partner validation required</t>
         </is>
       </c>
-      <c r="W55" s="9" t="n">
+      <c r="W55" s="5" t="n">
         <v>385896</v>
       </c>
-      <c r="X55" s="9" t="inlineStr">
+      <c r="X55" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y55" s="5" t="n">
+        <v>75747</v>
+      </c>
+      <c r="Z55" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA55" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB55" s="5" t="n">
+        <v>7575</v>
+      </c>
+      <c r="AC55" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD55" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -13797,12 +15213,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W56" s="9" t="n">
+      <c r="W56" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X56" s="9" t="inlineStr">
+      <c r="X56" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y56" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z56" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA56" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC56" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD56" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -13907,12 +15345,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W57" s="9" t="n">
+      <c r="W57" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X57" s="9" t="inlineStr">
+      <c r="X57" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y57" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z57" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA57" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB57" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC57" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD57" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -14017,12 +15477,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W58" s="9" t="n">
+      <c r="W58" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X58" s="9" t="inlineStr">
+      <c r="X58" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y58" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z58" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA58" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC58" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD58" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -14127,12 +15609,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W59" s="9" t="n">
+      <c r="W59" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X59" s="9" t="inlineStr">
+      <c r="X59" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y59" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z59" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA59" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC59" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD59" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -14237,12 +15741,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W60" s="9" t="n">
+      <c r="W60" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X60" s="9" t="inlineStr">
+      <c r="X60" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y60" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z60" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA60" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC60" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD60" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -14347,12 +15873,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W61" s="9" t="n">
+      <c r="W61" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X61" s="9" t="inlineStr">
+      <c r="X61" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y61" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z61" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA61" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC61" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD61" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -14457,12 +16005,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W62" s="9" t="n">
+      <c r="W62" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X62" s="9" t="inlineStr">
+      <c r="X62" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y62" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z62" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA62" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB62" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC62" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD62" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -14567,12 +16137,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W63" s="9" t="n">
+      <c r="W63" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X63" s="9" t="inlineStr">
+      <c r="X63" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y63" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z63" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA63" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB63" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC63" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD63" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -14677,12 +16269,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W64" s="9" t="n">
+      <c r="W64" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X64" s="9" t="inlineStr">
+      <c r="X64" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y64" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z64" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA64" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB64" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC64" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD64" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -14787,12 +16401,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W65" s="9" t="n">
+      <c r="W65" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X65" s="9" t="inlineStr">
+      <c r="X65" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y65" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z65" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA65" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB65" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC65" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD65" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -14897,12 +16533,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W66" s="9" t="n">
+      <c r="W66" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X66" s="9" t="inlineStr">
+      <c r="X66" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y66" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z66" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA66" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB66" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC66" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD66" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -15007,12 +16665,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W67" s="9" t="n">
+      <c r="W67" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X67" s="9" t="inlineStr">
+      <c r="X67" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y67" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z67" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA67" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB67" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC67" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD67" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -15117,12 +16797,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W68" s="9" t="n">
+      <c r="W68" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X68" s="9" t="inlineStr">
+      <c r="X68" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y68" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z68" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA68" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB68" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC68" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD68" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -15227,12 +16929,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W69" s="9" t="n">
+      <c r="W69" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X69" s="9" t="inlineStr">
+      <c r="X69" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y69" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z69" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA69" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB69" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC69" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD69" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -15337,12 +17061,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W70" s="9" t="n">
+      <c r="W70" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X70" s="9" t="inlineStr">
+      <c r="X70" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y70" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z70" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA70" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB70" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC70" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD70" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -15447,12 +17193,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W71" s="9" t="n">
+      <c r="W71" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X71" s="9" t="inlineStr">
+      <c r="X71" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y71" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z71" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA71" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB71" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC71" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD71" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -15557,12 +17325,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W72" s="9" t="n">
+      <c r="W72" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X72" s="9" t="inlineStr">
+      <c r="X72" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y72" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z72" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA72" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB72" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC72" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD72" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -15667,12 +17457,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W73" s="9" t="n">
+      <c r="W73" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X73" s="9" t="inlineStr">
+      <c r="X73" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y73" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z73" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA73" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB73" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC73" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD73" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -15777,12 +17589,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W74" s="9" t="n">
+      <c r="W74" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X74" s="9" t="inlineStr">
+      <c r="X74" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y74" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z74" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA74" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB74" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC74" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD74" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -15887,12 +17721,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W75" s="9" t="n">
+      <c r="W75" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X75" s="9" t="inlineStr">
+      <c r="X75" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y75" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z75" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA75" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB75" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC75" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD75" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -15997,12 +17853,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W76" s="9" t="n">
+      <c r="W76" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X76" s="9" t="inlineStr">
+      <c r="X76" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y76" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z76" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA76" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB76" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC76" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD76" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -16107,12 +17985,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W77" s="9" t="n">
+      <c r="W77" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X77" s="9" t="inlineStr">
+      <c r="X77" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y77" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z77" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA77" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB77" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC77" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD77" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -16217,12 +18117,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W78" s="9" t="n">
+      <c r="W78" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X78" s="9" t="inlineStr">
+      <c r="X78" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y78" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z78" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA78" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB78" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC78" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD78" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -16327,12 +18249,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W79" s="9" t="n">
+      <c r="W79" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X79" s="9" t="inlineStr">
+      <c r="X79" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y79" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z79" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA79" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB79" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC79" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD79" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -16437,12 +18381,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W80" s="9" t="n">
+      <c r="W80" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X80" s="9" t="inlineStr">
+      <c r="X80" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y80" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z80" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA80" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB80" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC80" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD80" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -16547,12 +18513,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W81" s="9" t="n">
+      <c r="W81" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X81" s="9" t="inlineStr">
+      <c r="X81" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y81" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z81" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA81" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB81" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC81" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD81" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -16657,12 +18645,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W82" s="9" t="n">
+      <c r="W82" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X82" s="9" t="inlineStr">
+      <c r="X82" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y82" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z82" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA82" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB82" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC82" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD82" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -16767,12 +18777,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W83" s="9" t="n">
+      <c r="W83" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X83" s="9" t="inlineStr">
+      <c r="X83" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y83" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z83" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA83" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB83" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC83" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD83" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -16877,12 +18909,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W84" s="9" t="n">
+      <c r="W84" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X84" s="9" t="inlineStr">
+      <c r="X84" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y84" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z84" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA84" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB84" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC84" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD84" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -16987,12 +19041,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W85" s="9" t="n">
+      <c r="W85" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X85" s="9" t="inlineStr">
+      <c r="X85" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y85" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z85" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA85" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB85" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC85" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD85" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -17097,12 +19173,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W86" s="9" t="n">
+      <c r="W86" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X86" s="9" t="inlineStr">
+      <c r="X86" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y86" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z86" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA86" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB86" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC86" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD86" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -17207,12 +19305,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W87" s="9" t="n">
+      <c r="W87" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X87" s="9" t="inlineStr">
+      <c r="X87" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y87" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z87" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA87" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB87" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC87" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD87" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -17317,12 +19437,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W88" s="9" t="n">
+      <c r="W88" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X88" s="9" t="inlineStr">
+      <c r="X88" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y88" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z88" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA88" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB88" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC88" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD88" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -17427,12 +19569,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W89" s="9" t="n">
+      <c r="W89" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X89" s="9" t="inlineStr">
+      <c r="X89" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y89" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z89" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA89" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB89" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC89" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD89" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -17537,12 +19701,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W90" s="9" t="n">
+      <c r="W90" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X90" s="9" t="inlineStr">
+      <c r="X90" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y90" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z90" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA90" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB90" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC90" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD90" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -17647,12 +19833,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W91" s="9" t="n">
+      <c r="W91" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X91" s="9" t="inlineStr">
+      <c r="X91" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y91" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z91" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA91" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB91" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC91" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD91" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -17757,12 +19965,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W92" s="9" t="n">
+      <c r="W92" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X92" s="9" t="inlineStr">
+      <c r="X92" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y92" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z92" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA92" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB92" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC92" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD92" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -17867,12 +20097,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W93" s="9" t="n">
+      <c r="W93" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X93" s="9" t="inlineStr">
+      <c r="X93" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y93" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z93" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA93" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB93" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC93" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD93" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -17977,12 +20229,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W94" s="9" t="n">
+      <c r="W94" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X94" s="9" t="inlineStr">
+      <c r="X94" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y94" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z94" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA94" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB94" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC94" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD94" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -18087,12 +20361,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W95" s="9" t="n">
+      <c r="W95" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X95" s="9" t="inlineStr">
+      <c r="X95" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y95" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z95" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA95" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB95" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC95" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD95" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -18197,12 +20493,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W96" s="9" t="n">
+      <c r="W96" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X96" s="9" t="inlineStr">
+      <c r="X96" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y96" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z96" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA96" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB96" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC96" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD96" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -18307,12 +20625,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W97" s="9" t="n">
+      <c r="W97" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X97" s="9" t="inlineStr">
+      <c r="X97" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y97" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z97" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA97" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB97" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC97" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD97" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -18417,12 +20757,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W98" s="9" t="n">
+      <c r="W98" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X98" s="9" t="inlineStr">
+      <c r="X98" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y98" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z98" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA98" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB98" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC98" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD98" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -18527,12 +20889,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W99" s="9" t="n">
+      <c r="W99" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X99" s="9" t="inlineStr">
+      <c r="X99" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y99" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z99" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA99" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB99" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC99" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD99" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -18637,12 +21021,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W100" s="9" t="n">
+      <c r="W100" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X100" s="9" t="inlineStr">
+      <c r="X100" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y100" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z100" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA100" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB100" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC100" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD100" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -18747,12 +21153,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W101" s="9" t="n">
+      <c r="W101" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X101" s="9" t="inlineStr">
+      <c r="X101" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y101" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z101" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA101" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB101" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC101" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD101" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -18857,12 +21285,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W102" s="9" t="n">
+      <c r="W102" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X102" s="9" t="inlineStr">
+      <c r="X102" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y102" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z102" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA102" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB102" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC102" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD102" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -18967,12 +21417,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W103" s="9" t="n">
+      <c r="W103" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X103" s="9" t="inlineStr">
+      <c r="X103" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y103" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z103" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA103" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB103" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC103" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD103" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -19077,12 +21549,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W104" s="9" t="n">
+      <c r="W104" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X104" s="9" t="inlineStr">
+      <c r="X104" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y104" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z104" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA104" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB104" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC104" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD104" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -19187,12 +21681,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W105" s="9" t="n">
+      <c r="W105" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X105" s="9" t="inlineStr">
+      <c r="X105" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y105" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z105" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA105" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB105" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC105" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD105" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -19297,12 +21813,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W106" s="9" t="n">
+      <c r="W106" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X106" s="9" t="inlineStr">
+      <c r="X106" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y106" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z106" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA106" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB106" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC106" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD106" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -19407,12 +21945,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W107" s="9" t="n">
+      <c r="W107" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X107" s="9" t="inlineStr">
+      <c r="X107" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y107" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z107" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA107" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB107" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC107" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD107" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -19517,12 +22077,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W108" s="9" t="n">
+      <c r="W108" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X108" s="9" t="inlineStr">
+      <c r="X108" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y108" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z108" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA108" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB108" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC108" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD108" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -19627,12 +22209,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W109" s="9" t="n">
+      <c r="W109" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X109" s="9" t="inlineStr">
+      <c r="X109" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y109" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z109" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA109" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB109" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC109" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD109" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -19737,12 +22341,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W110" s="9" t="n">
+      <c r="W110" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X110" s="9" t="inlineStr">
+      <c r="X110" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y110" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z110" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA110" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB110" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC110" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD110" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -19847,12 +22473,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W111" s="9" t="n">
+      <c r="W111" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X111" s="9" t="inlineStr">
+      <c r="X111" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y111" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z111" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA111" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB111" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC111" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD111" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -19957,12 +22605,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W112" s="9" t="n">
+      <c r="W112" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X112" s="9" t="inlineStr">
+      <c r="X112" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y112" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z112" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA112" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB112" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC112" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD112" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -20067,12 +22737,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W113" s="9" t="n">
+      <c r="W113" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X113" s="9" t="inlineStr">
+      <c r="X113" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y113" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z113" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA113" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB113" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC113" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD113" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -20177,12 +22869,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W114" s="9" t="n">
+      <c r="W114" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X114" s="9" t="inlineStr">
+      <c r="X114" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y114" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z114" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA114" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB114" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC114" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD114" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -20287,12 +23001,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W115" s="9" t="n">
+      <c r="W115" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X115" s="9" t="inlineStr">
+      <c r="X115" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y115" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z115" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA115" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB115" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC115" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD115" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -20397,12 +23133,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W116" s="9" t="n">
+      <c r="W116" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X116" s="9" t="inlineStr">
+      <c r="X116" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y116" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z116" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA116" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB116" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC116" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD116" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -20507,12 +23265,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W117" s="9" t="n">
+      <c r="W117" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X117" s="9" t="inlineStr">
+      <c r="X117" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y117" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z117" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA117" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB117" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC117" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD117" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -20617,12 +23397,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W118" s="9" t="n">
+      <c r="W118" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X118" s="9" t="inlineStr">
+      <c r="X118" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y118" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z118" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA118" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB118" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC118" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD118" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -20727,12 +23529,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W119" s="9" t="n">
+      <c r="W119" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X119" s="9" t="inlineStr">
+      <c r="X119" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y119" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z119" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA119" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB119" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC119" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD119" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -20837,12 +23661,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W120" s="9" t="n">
+      <c r="W120" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X120" s="9" t="inlineStr">
+      <c r="X120" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y120" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z120" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA120" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB120" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC120" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD120" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -20947,12 +23793,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W121" s="9" t="n">
+      <c r="W121" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X121" s="9" t="inlineStr">
+      <c r="X121" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y121" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z121" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA121" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB121" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC121" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD121" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -21057,12 +23925,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W122" s="9" t="n">
+      <c r="W122" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X122" s="9" t="inlineStr">
+      <c r="X122" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y122" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z122" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA122" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB122" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC122" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD122" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -21167,12 +24057,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W123" s="9" t="n">
+      <c r="W123" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X123" s="9" t="inlineStr">
+      <c r="X123" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y123" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z123" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA123" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB123" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC123" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD123" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -21277,12 +24189,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W124" s="9" t="n">
+      <c r="W124" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X124" s="9" t="inlineStr">
+      <c r="X124" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y124" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z124" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA124" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB124" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC124" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD124" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -21387,12 +24321,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W125" s="9" t="n">
+      <c r="W125" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X125" s="9" t="inlineStr">
+      <c r="X125" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y125" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z125" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA125" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB125" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC125" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD125" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -21497,12 +24453,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W126" s="9" t="n">
+      <c r="W126" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X126" s="9" t="inlineStr">
+      <c r="X126" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y126" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z126" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA126" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB126" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC126" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD126" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -21607,12 +24585,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W127" s="9" t="n">
+      <c r="W127" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X127" s="9" t="inlineStr">
+      <c r="X127" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y127" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z127" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA127" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB127" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC127" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD127" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -21717,12 +24717,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W128" s="9" t="n">
+      <c r="W128" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X128" s="9" t="inlineStr">
+      <c r="X128" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y128" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z128" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA128" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB128" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC128" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD128" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -21827,12 +24849,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W129" s="9" t="n">
+      <c r="W129" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X129" s="9" t="inlineStr">
+      <c r="X129" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y129" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z129" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA129" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB129" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC129" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD129" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -21937,12 +24981,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W130" s="9" t="n">
+      <c r="W130" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X130" s="9" t="inlineStr">
+      <c r="X130" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y130" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z130" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA130" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB130" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC130" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD130" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -22047,12 +25113,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W131" s="9" t="n">
+      <c r="W131" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X131" s="9" t="inlineStr">
+      <c r="X131" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y131" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z131" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA131" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB131" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC131" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD131" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -22157,12 +25245,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W132" s="9" t="n">
+      <c r="W132" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X132" s="9" t="inlineStr">
+      <c r="X132" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y132" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z132" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA132" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB132" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC132" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD132" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -22267,12 +25377,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W133" s="9" t="n">
+      <c r="W133" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X133" s="9" t="inlineStr">
+      <c r="X133" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y133" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z133" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA133" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB133" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC133" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD133" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -22377,12 +25509,34 @@
           <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
         </is>
       </c>
-      <c r="W134" s="9" t="n">
+      <c r="W134" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X134" s="9" t="inlineStr">
+      <c r="X134" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y134" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z134" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA134" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB134" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC134" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD134" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -22491,12 +25645,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W135" s="9" t="n">
+      <c r="W135" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X135" s="9" t="inlineStr">
+      <c r="X135" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y135" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="Z135" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA135" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB135" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC135" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD135" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -22605,12 +25781,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W136" s="9" t="n">
+      <c r="W136" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X136" s="9" t="inlineStr">
+      <c r="X136" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y136" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z136" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA136" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB136" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC136" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD136" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -22719,12 +25917,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W137" s="9" t="n">
+      <c r="W137" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X137" s="9" t="inlineStr">
+      <c r="X137" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y137" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z137" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA137" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB137" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC137" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD137" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -22833,12 +26053,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W138" s="9" t="n">
+      <c r="W138" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X138" s="9" t="inlineStr">
+      <c r="X138" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y138" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z138" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA138" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB138" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC138" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD138" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -22947,12 +26189,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W139" s="9" t="n">
+      <c r="W139" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X139" s="9" t="inlineStr">
+      <c r="X139" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y139" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z139" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA139" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB139" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC139" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD139" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -23061,12 +26325,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W140" s="9" t="n">
+      <c r="W140" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X140" s="9" t="inlineStr">
+      <c r="X140" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y140" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="Z140" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA140" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB140" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="AC140" s="5" t="inlineStr">
+        <is>
+          <t>Scenario estimate = WorldPop population within 5 km × 10%; validate with partner target/assessment</t>
+        </is>
+      </c>
+      <c r="AD140" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -23175,12 +26461,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W141" s="9" t="n">
+      <c r="W141" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X141" s="9" t="inlineStr">
+      <c r="X141" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y141" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z141" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA141" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB141" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC141" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD141" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -23287,12 +26595,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W142" s="9" t="n">
+      <c r="W142" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X142" s="9" t="inlineStr">
+      <c r="X142" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y142" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z142" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA142" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB142" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC142" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD142" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -23399,12 +26729,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W143" s="9" t="n">
+      <c r="W143" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X143" s="9" t="inlineStr">
+      <c r="X143" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y143" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z143" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA143" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB143" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC143" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD143" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -23505,12 +26857,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W144" s="9" t="n">
+      <c r="W144" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X144" s="9" t="inlineStr">
+      <c r="X144" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y144" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z144" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA144" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB144" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC144" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD144" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -23611,12 +26985,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W145" s="9" t="n">
+      <c r="W145" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X145" s="9" t="inlineStr">
+      <c r="X145" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y145" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z145" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA145" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB145" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC145" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD145" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -23725,12 +27121,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W146" s="9" t="n">
+      <c r="W146" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X146" s="9" t="inlineStr">
+      <c r="X146" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y146" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z146" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA146" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB146" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC146" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD146" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -23839,12 +27257,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W147" s="9" t="n">
+      <c r="W147" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X147" s="9" t="inlineStr">
+      <c r="X147" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y147" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z147" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA147" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB147" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC147" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD147" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -23953,12 +27393,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W148" s="9" t="n">
+      <c r="W148" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X148" s="9" t="inlineStr">
+      <c r="X148" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y148" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z148" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA148" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB148" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC148" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD148" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -24067,12 +27529,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W149" s="9" t="n">
+      <c r="W149" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X149" s="9" t="inlineStr">
+      <c r="X149" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y149" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z149" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA149" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB149" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC149" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD149" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -24181,12 +27665,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W150" s="9" t="n">
+      <c r="W150" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X150" s="9" t="inlineStr">
+      <c r="X150" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y150" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z150" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA150" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB150" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC150" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD150" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -24295,12 +27801,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W151" s="9" t="n">
+      <c r="W151" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X151" s="9" t="inlineStr">
+      <c r="X151" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y151" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z151" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA151" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB151" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC151" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD151" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -24409,12 +27937,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W152" s="9" t="n">
+      <c r="W152" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X152" s="9" t="inlineStr">
+      <c r="X152" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y152" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Z152" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA152" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB152" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC152" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD152" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -24523,12 +28073,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W153" s="9" t="n">
+      <c r="W153" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X153" s="9" t="inlineStr">
+      <c r="X153" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y153" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z153" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA153" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB153" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC153" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD153" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -24637,12 +28209,34 @@
           <t>https://data.humdata.org/dataset/ff5b9401-6c1e-4aa3-89e7-061f9a351b20/resource/9f3661ed-7512-4fae-bd2b-fad4d088dcbe/download/compilation-3w-de-projets-en-cours-01052018-2.xlsx</t>
         </is>
       </c>
-      <c r="W154" s="9" t="n">
+      <c r="W154" s="5" t="n">
         <v>309169</v>
       </c>
-      <c r="X154" s="9" t="inlineStr">
+      <c r="X154" s="5" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+      <c r="Y154" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z154" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA154" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB154" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC154" s="5" t="inlineStr">
+        <is>
+          <t>LOW RESULT: reference coordinate or locality boundary requires validation; scenario estimate only</t>
+        </is>
+      </c>
+      <c r="AD154" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
         </is>
       </c>
     </row>
@@ -24656,6 +28250,480 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="100" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="60" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Locality</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>WorldPop Population (2024)</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Radius used (km)</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Planning factor</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Estimated beneficiaries per intervention</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Method / limitation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Andrada</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>2103</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Sum of WorldPop raster cells intersecting a 5 km circle around the workbook reference coordinate; approximate locality denominator, not an official boundary or beneficiary count</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Babombi</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>236</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Sum of WorldPop raster cells intersecting a 5 km circle around the workbook reference coordinate; approximate locality denominator, not an official boundary or beneficiary count</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Bafwabete</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Sum of WorldPop raster cells intersecting a 5 km circle around the workbook reference coordinate; approximate locality denominator, not an official boundary or beneficiary count</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Biakato</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>669</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Sum of WorldPop raster cells intersecting a 5 km circle around the workbook reference coordinate; approximate locality denominator, not an official boundary or beneficiary count</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Durba</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>73911</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7391</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Sum of WorldPop raster cells intersecting a 5 km circle around the workbook reference coordinate; approximate locality denominator, not an official boundary or beneficiary count</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Ibambi</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Sum of WorldPop raster cells intersecting a 5 km circle around the workbook reference coordinate; approximate locality denominator, not an official boundary or beneficiary count</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Lolwa</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Sum of WorldPop raster cells intersecting a 5 km circle around the workbook reference coordinate; approximate locality denominator, not an official boundary or beneficiary count</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Sum of WorldPop raster cells intersecting a 5 km circle around the workbook reference coordinate; approximate locality denominator, not an official boundary or beneficiary count</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa Centre</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Sum of WorldPop raster cells intersecting a 5 km circle around the workbook reference coordinate; approximate locality denominator, not an official boundary or beneficiary count</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Mandima</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>4247</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Sum of WorldPop raster cells intersecting a 5 km circle around the workbook reference coordinate; approximate locality denominator, not an official boundary or beneficiary count</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Nia-Nia</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Sum of WorldPop raster cells intersecting a 5 km circle around the workbook reference coordinate; approximate locality denominator, not an official boundary or beneficiary count</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Nyangwe</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>106896</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>10690</v>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Sum of WorldPop raster cells intersecting a 5 km circle around the workbook reference coordinate; approximate locality denominator, not an official boundary or beneficiary count</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Pawa</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>13082</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1308</v>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Sum of WorldPop raster cells intersecting a 5 km circle around the workbook reference coordinate; approximate locality denominator, not an official boundary or beneficiary count</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Wamba Centre</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>52598</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5260</v>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Sum of WorldPop raster cells intersecting a 5 km circle around the workbook reference coordinate; approximate locality denominator, not an official boundary or beneficiary count</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Watsa Centre</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>75747</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>7575</v>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Sum of WorldPop raster cells intersecting a 5 km circle around the workbook reference coordinate; approximate locality denominator, not an official boundary or beneficiary count</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>WorldPop, University of Southampton, DRC constrained population raster 2024, R2025A v1, 100 m</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>https://data.worldpop.org/GIS/Population/Global_2015_2030/R2025A/2024/COD/v1/100m/constrained/cod_pop_2024_CN_100m_R2025A_v1.tif</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Estimated beneficiaries / intervention = WorldPop locality population × 10% planning coverage factor</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Replace the 10% factor with partner-approved beneficiary targets or needs-assessment coverage before reporting. Avoid summing rows across interventions because the same population may be counted more than once.</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40830,7 +44898,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40968,7 +45036,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -56066,7 +60134,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -57289,7 +61357,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -57657,13 +61725,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -57934,158 +62002,19 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WorldPop beneficiary scenario</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Locality population is estimated from the WorldPop 2024 DRC 100 m raster within a 5 km circle around each workbook reference point. Estimated beneficiaries per intervention use a 10% planning factor. These are not observed beneficiaries and must be replaced or validated with partner targets.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="90" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="42" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>Publisher</t>
-        </is>
-      </c>
-      <c r="C1" s="13" t="inlineStr">
-        <is>
-          <t>Coverage / use</t>
-        </is>
-      </c>
-      <c r="D1" s="13" t="inlineStr">
-        <is>
-          <t>Publication / extract date</t>
-        </is>
-      </c>
-      <c r="E1" s="13" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="F1" s="13" t="inlineStr">
-        <is>
-          <t>Use in workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>République Démocratique du Congo : Présence Opérationnelle</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>OCHA Democratic Republic of the Congo / HDX</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>Operational presence (projects, dates, territory, province, actor and cluster); Admin 3 registry</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>Extract February 2026; dataset range 2022-2026</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>https://data.humdata.org/dataset/49f93973-5f8e-4a89-9bbb-43db497c7255/resource/162c439d-5c9b-494a-b769-33c30c4eab8e/download/extrait-fev-2026.xlsx</t>
-        </is>
-      </c>
-      <c r="F2" s="9" t="inlineStr">
-        <is>
-          <t>Verified Mambasa records and operation dates</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>DRC - 3 W National - Mai 2018</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>OCHA Democratic Republic of the Congo / HDX</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Historical 3W project compilation</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>https://data.humdata.org/dataset/drc-3-w-national-mai-2018</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>Background reference only; not used to assert current presence</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>DRC Displacement Data - Ituri Province - Baseline Assessment</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>IOM DTM / HDX</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>Displacement and needs data, including Mambasa territory</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>Current cycle July 2026</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>https://data.humdata.org/dataset/drc-displacement-data-ituri-province-baseline-assessment-iom-dtm</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>Contextual reference; not an organisation-operations source</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F4"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/RFO_Stakeholders Final.xlsx
+++ b/RFO_Stakeholders Final.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RFO_Stakeholders Final" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="5Ws MODEL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="WorldPop Estimates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4Ws MODEL" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5Ws Guide" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="5Ws Database" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="RFO STAKEHOLDER HISTORY" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Coverage Summary" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Data Notes" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Data Sources" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Historical Coverage" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="3W Matrix (Who does What Where)" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Cluster Summary (Who Does What)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFO_Stakeholders Final" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5Ws MODEL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WorldPop Estimates" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4Ws MODEL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5Ws Guide" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5Ws Database" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFO STAKEHOLDER HISTORY" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage Summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Notes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Sources" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical Coverage" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3W Matrix (Who does What Where)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cluster Summary (Who Does What)" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RFO_Stakeholders Final'!$A$1:$T$29</definedName>
@@ -4276,7 +4276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4447,6 +4447,38 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ebola response evidence: UNICEF EOC and INSP/INRB BDBV public data</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UNICEF EOC; DRC Ministry of Health/INSP/INRB; WHO-supported response</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Historical 2018-2019 Ebola response records in Mambasa/Mandima health zones and preliminary 2026 BDBV response records in Mambasa and Wamba; no verified Watsa-specific operation identified</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2019 historical extracts and 2026 preliminary public monitoring data</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://data.humdata.org/dataset/unicef-eoc-2018-2019-dashboard-en-final; https://github.com/INRB-UMIE/BDBV2026-Data</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ebola response activities, surveillance, psychosocial support, IPC, points of control, laboratory readiness and community engagement</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4459,7 +4491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4624,6 +4656,33 @@
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Latest workbook date; not a new source reporting period</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2018-2026 Ebola response</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>UNICEF EOC historical datasets and INSP/INRB BDBV public monitoring</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>9 source-backed 5Ws records</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mambasa (Mambasa/Mandima health zones) and Wamba; no Watsa-specific verified record</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Health-zone geography is a proxy; 2026 BDBV data are preliminary and require partner/government validation</t>
         </is>
       </c>
     </row>
@@ -7899,7 +7958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD154"/>
+  <dimension ref="A1:AD164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28237,6 +28296,1526 @@
       <c r="AD154" s="5" t="inlineStr">
         <is>
           <t>WorldPop 2024 DRC R2025A v1, 100 m constrained raster (DOI: 10.5258/SOTON/WP00839)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>EB-2019-001</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF Ebola Emergency Operations Centre</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>UN agency</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Surveillance</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>Ebola case surveillance and line-list reporting in Mandima Health Zone</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>Support outbreak surveillance, case investigation and response coordination in an affected health zone</t>
+        </is>
+      </c>
+      <c r="G155" s="14" t="inlineStr">
+        <is>
+          <t>2018-08-05</t>
+        </is>
+      </c>
+      <c r="H155" s="14" t="inlineStr">
+        <is>
+          <t>2019-08-05</t>
+        </is>
+      </c>
+      <c r="I155" s="5" t="inlineStr">
+        <is>
+          <t>2018-2019</t>
+        </is>
+      </c>
+      <c r="J155" s="5" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="L155" s="5" t="inlineStr">
+        <is>
+          <t>Mandima</t>
+        </is>
+      </c>
+      <c r="M155" s="5" t="inlineStr">
+        <is>
+          <t>Mandima Health Zone</t>
+        </is>
+      </c>
+      <c r="N155" s="5" t="inlineStr">
+        <is>
+          <t>0.87° N, 29.75° E</t>
+        </is>
+      </c>
+      <c r="O155" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P155" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q155" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="R155" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="S155" s="5" t="inlineStr">
+        <is>
+          <t>Historical verified</t>
+        </is>
+      </c>
+      <c r="T155" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF EOC annual dashboard: 238 Mandima line-list records (234 confirmed, 4 probable); health-zone geography used as Mambasa Territory proxy</t>
+        </is>
+      </c>
+      <c r="U155" s="5" t="inlineStr">
+        <is>
+          <t>Approximate health-zone reference; territory assignment requires validation</t>
+        </is>
+      </c>
+      <c r="V155" s="5" t="inlineStr">
+        <is>
+          <t>https://data.humdata.org/dataset/unicef-eoc-2018-2019-dashboard-en-final</t>
+        </is>
+      </c>
+      <c r="W155" s="5" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="X155" s="5" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+      <c r="Y155" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="Z155" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AA155" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AB155" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="AC155" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response record; beneficiary estimate not calculated</t>
+        </is>
+      </c>
+      <c r="AD155" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable for response activity record</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>EB-2019-002</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF Ebola Emergency Operations Centre</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>UN agency</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Surveillance</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>Ebola case investigation and line-list reporting in Mambasa Health Zone</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>Detect, investigate and refer suspected and confirmed Ebola cases</t>
+        </is>
+      </c>
+      <c r="G156" s="14" t="inlineStr">
+        <is>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="H156" s="14" t="inlineStr">
+        <is>
+          <t>2019-08-05</t>
+        </is>
+      </c>
+      <c r="I156" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J156" s="5" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="L156" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="M156" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa Health Zone</t>
+        </is>
+      </c>
+      <c r="N156" s="5" t="inlineStr">
+        <is>
+          <t>1.55° N, 27.20° E</t>
+        </is>
+      </c>
+      <c r="O156" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P156" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q156" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="R156" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="S156" s="5" t="inlineStr">
+        <is>
+          <t>Historical verified</t>
+        </is>
+      </c>
+      <c r="T156" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF EOC annual dashboard records 9 confirmed Mambasa-zone cases; health-zone geography used as territory proxy</t>
+        </is>
+      </c>
+      <c r="U156" s="5" t="inlineStr">
+        <is>
+          <t>Approximate health-zone reference; case counts are not beneficiary counts</t>
+        </is>
+      </c>
+      <c r="V156" s="5" t="inlineStr">
+        <is>
+          <t>https://data.humdata.org/dataset/unicef-eoc-2018-2019-dashboard-en-final</t>
+        </is>
+      </c>
+      <c r="W156" s="5" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="X156" s="5" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+      <c r="Y156" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="Z156" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AA156" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AB156" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="AC156" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response record; beneficiary estimate not calculated</t>
+        </is>
+      </c>
+      <c r="AD156" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable for response activity record</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>EB-2019-003</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF Ebola Emergency Operations Centre</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>UN agency</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Psychosocial and protection</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>Psychosocial support, child protection and family support during Ebola response</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>Reduce psychosocial harm and protect children and families affected by Ebola</t>
+        </is>
+      </c>
+      <c r="G157" s="14" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="H157" s="14" t="inlineStr">
+        <is>
+          <t>2019-04-30</t>
+        </is>
+      </c>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="L157" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa / Mandima</t>
+        </is>
+      </c>
+      <c r="M157" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa and Mandima Health Zones</t>
+        </is>
+      </c>
+      <c r="N157" s="5" t="inlineStr">
+        <is>
+          <t>1.21° N, 28.48° E</t>
+        </is>
+      </c>
+      <c r="O157" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P157" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q157" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="R157" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="S157" s="5" t="inlineStr">
+        <is>
+          <t>Historical verified</t>
+        </is>
+      </c>
+      <c r="T157" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF April 2019 psychosocial pillar database records CTE/CT support, psychoeducation and family assistance in both health zones</t>
+        </is>
+      </c>
+      <c r="U157" s="5" t="inlineStr">
+        <is>
+          <t>Approximate combined health-zone reference; validate locality-specific coverage</t>
+        </is>
+      </c>
+      <c r="V157" s="5" t="inlineStr">
+        <is>
+          <t>https://data.humdata.org/dataset/ebola-unicef-eoc-psychosocial-pillar-database-drc-april-2019</t>
+        </is>
+      </c>
+      <c r="W157" s="5" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="X157" s="5" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+      <c r="Y157" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="Z157" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AA157" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AB157" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="AC157" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response record; beneficiary estimate not calculated</t>
+        </is>
+      </c>
+      <c r="AD157" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable for response activity record</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>EB-2019-004</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF Ebola Emergency Operations Centre</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>UN agency</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Psychosocial, protection and nutrition</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>Psychosocial support, separated-child assistance and nutrition support</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>Protect children and provide family and nutrition support during Ebola response</t>
+        </is>
+      </c>
+      <c r="G158" s="14" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="H158" s="14" t="inlineStr">
+        <is>
+          <t>2019-05-31</t>
+        </is>
+      </c>
+      <c r="I158" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J158" s="5" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="L158" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa / Mandima</t>
+        </is>
+      </c>
+      <c r="M158" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa and Mandima Health Zones</t>
+        </is>
+      </c>
+      <c r="N158" s="5" t="inlineStr">
+        <is>
+          <t>1.21° N, 28.48° E</t>
+        </is>
+      </c>
+      <c r="O158" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P158" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q158" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="R158" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="S158" s="5" t="inlineStr">
+        <is>
+          <t>Historical verified</t>
+        </is>
+      </c>
+      <c r="T158" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF May 2019 psychosocial database records CTE support, contact/family follow-up and food/nutrition kit distribution in both zones</t>
+        </is>
+      </c>
+      <c r="U158" s="5" t="inlineStr">
+        <is>
+          <t>Approximate combined health-zone reference; validate locality-specific coverage</t>
+        </is>
+      </c>
+      <c r="V158" s="5" t="inlineStr">
+        <is>
+          <t>https://data.humdata.org/dataset/unicef-eoc-psychosocial-mai-2019-dataset</t>
+        </is>
+      </c>
+      <c r="W158" s="5" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="X158" s="5" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+      <c r="Y158" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="Z158" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AA158" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AB158" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="AC158" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response record; beneficiary estimate not calculated</t>
+        </is>
+      </c>
+      <c r="AD158" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable for response activity record</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>EB-2019-005</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF Ebola Emergency Operations Centre</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>UN agency</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Psychosocial and protection</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>Psychosocial support, contact/family follow-up and child protection</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>Support affected people, contacts, families and children during outbreak response</t>
+        </is>
+      </c>
+      <c r="G159" s="14" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="H159" s="14" t="inlineStr">
+        <is>
+          <t>2019-06-30</t>
+        </is>
+      </c>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J159" s="5" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="L159" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa / Mandima</t>
+        </is>
+      </c>
+      <c r="M159" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa and Mandima Health Zones</t>
+        </is>
+      </c>
+      <c r="N159" s="5" t="inlineStr">
+        <is>
+          <t>1.21° N, 28.48° E</t>
+        </is>
+      </c>
+      <c r="O159" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P159" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q159" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="R159" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="S159" s="5" t="inlineStr">
+        <is>
+          <t>Historical verified</t>
+        </is>
+      </c>
+      <c r="T159" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF June 2019 psychosocial database records support for suspected/confirmed cases, contacts, families and children</t>
+        </is>
+      </c>
+      <c r="U159" s="5" t="inlineStr">
+        <is>
+          <t>Approximate combined health-zone reference; validate locality-specific coverage</t>
+        </is>
+      </c>
+      <c r="V159" s="5" t="inlineStr">
+        <is>
+          <t>https://data.humdata.org/dataset/unicef-eoc-psychosocial-juin-2019-dataset</t>
+        </is>
+      </c>
+      <c r="W159" s="5" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="X159" s="5" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+      <c r="Y159" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="Z159" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AA159" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AB159" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="AC159" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response record; beneficiary estimate not calculated</t>
+        </is>
+      </c>
+      <c r="AD159" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable for response activity record</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>EB-2026-001</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>INSP / INRB BDBV response</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>Government / public health</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Surveillance</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>Routine surveillance, alerts, investigations, active case finding and contact follow-up</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>Detect and contain suspected Bundibugyo virus transmission in Mambasa</t>
+        </is>
+      </c>
+      <c r="G160" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="H160" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J160" s="5" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="L160" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="M160" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa Health Zone</t>
+        </is>
+      </c>
+      <c r="N160" s="5" t="inlineStr">
+        <is>
+          <t>1.55° N, 27.20° E</t>
+        </is>
+      </c>
+      <c r="O160" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P160" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q160" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="R160" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="S160" s="5" t="inlineStr">
+        <is>
+          <t>Current preliminary</t>
+        </is>
+      </c>
+      <c r="T160" s="5" t="inlineStr">
+        <is>
+          <t>INSP/INRB public response monitoring records surveillance and investigations in Mambasa; preliminary sitrep-derived data</t>
+        </is>
+      </c>
+      <c r="U160" s="5" t="inlineStr">
+        <is>
+          <t>Approximate health-zone reference; BDBV records require routine official validation</t>
+        </is>
+      </c>
+      <c r="V160" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/INRB-UMIE/BDBV2026-Data/blob/main/data/public_health_response/processed/public_health_response__epidemiological_monitoring_en__daily.csv</t>
+        </is>
+      </c>
+      <c r="W160" s="5" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="X160" s="5" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+      <c r="Y160" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="Z160" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AA160" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AB160" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="AC160" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response record; beneficiary estimate not calculated</t>
+        </is>
+      </c>
+      <c r="AD160" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable for response activity record</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>EB-2026-002</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>INSP / INRB BDBV response</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>Government / public health</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Infection prevention and control</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>IPC briefings, WASH and IPC kit distribution for Mambasa providers</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>Reduce healthcare-associated transmission through IPC and WASH readiness</t>
+        </is>
+      </c>
+      <c r="G161" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H161" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="I161" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J161" s="5" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="L161" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="M161" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa Health Zone</t>
+        </is>
+      </c>
+      <c r="N161" s="5" t="inlineStr">
+        <is>
+          <t>1.55° N, 27.20° E</t>
+        </is>
+      </c>
+      <c r="O161" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P161" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q161" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="R161" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="S161" s="5" t="inlineStr">
+        <is>
+          <t>Current preliminary</t>
+        </is>
+      </c>
+      <c r="T161" s="5" t="inlineStr">
+        <is>
+          <t>INSP/INRB public response monitoring records provider briefings and IPC/WASH kit support in Mambasa</t>
+        </is>
+      </c>
+      <c r="U161" s="5" t="inlineStr">
+        <is>
+          <t>Approximate health-zone reference; BDBV records are preliminary</t>
+        </is>
+      </c>
+      <c r="V161" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/INRB-UMIE/BDBV2026-Data/blob/main/data/public_health_response/processed/public_health_response__epidemiological_infection_prevention_controle_en__daily.csv</t>
+        </is>
+      </c>
+      <c r="W161" s="5" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="X161" s="5" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+      <c r="Y161" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="Z161" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AA161" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AB161" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="AC161" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response record; beneficiary estimate not calculated</t>
+        </is>
+      </c>
+      <c r="AD161" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable for response activity record</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>EB-2026-003</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>INSP / INRB BDBV response</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>Government / public health</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Points of control and laboratory preparedness</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>Activation of points of control, referrals and laboratory preparedness</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>Strengthen early detection, referral and diagnostic readiness in Mambasa</t>
+        </is>
+      </c>
+      <c r="G162" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H162" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="I162" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J162" s="5" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="L162" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="M162" s="5" t="inlineStr">
+        <is>
+          <t>Mabake / Mambasa points of control and Mambasa Health Zone</t>
+        </is>
+      </c>
+      <c r="N162" s="5" t="inlineStr">
+        <is>
+          <t>1.55° N, 27.20° E</t>
+        </is>
+      </c>
+      <c r="O162" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P162" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q162" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="R162" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="S162" s="5" t="inlineStr">
+        <is>
+          <t>Current preliminary</t>
+        </is>
+      </c>
+      <c r="T162" s="5" t="inlineStr">
+        <is>
+          <t>INSP/INRB provincial monitoring records PoC activation, referrals and laboratory installations; WHO-supported supplies are noted in logistics records</t>
+        </is>
+      </c>
+      <c r="U162" s="5" t="inlineStr">
+        <is>
+          <t>Approximate operational reference; names and boundaries require partner validation</t>
+        </is>
+      </c>
+      <c r="V162" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/INRB-UMIE/BDBV2026-Data/blob/main/data/public_health_response/processed/public_health_response__provincial_epidemiological_monitoring_en__daily.csv</t>
+        </is>
+      </c>
+      <c r="W162" s="5" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="X162" s="5" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+      <c r="Y162" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="Z162" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AA162" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AB162" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="AC162" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response record; beneficiary estimate not calculated</t>
+        </is>
+      </c>
+      <c r="AD162" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable for response activity record</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>EB-2026-004</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>INSP / DRC public health response</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>Government / public health</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Surveillance</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>BDBV case surveillance and cumulative case/death monitoring</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>Monitor and coordinate response to confirmed Bundibugyo virus transmission in Wamba</t>
+        </is>
+      </c>
+      <c r="G163" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H163" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="I163" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J163" s="5" t="inlineStr">
+        <is>
+          <t>Haut-Uele</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="inlineStr">
+        <is>
+          <t>Wamba</t>
+        </is>
+      </c>
+      <c r="L163" s="5" t="inlineStr">
+        <is>
+          <t>Wamba</t>
+        </is>
+      </c>
+      <c r="M163" s="5" t="inlineStr">
+        <is>
+          <t>Wamba Health Zone</t>
+        </is>
+      </c>
+      <c r="N163" s="5" t="inlineStr">
+        <is>
+          <t>2.14° N, 27.99° E</t>
+        </is>
+      </c>
+      <c r="O163" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="P163" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q163" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="R163" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="S163" s="5" t="inlineStr">
+        <is>
+          <t>Current preliminary</t>
+        </is>
+      </c>
+      <c r="T163" s="5" t="inlineStr">
+        <is>
+          <t>INSP/INRB-derived cumulative series reports Wamba first confirmed case on 10 July and 83 confirmed cases/31 deaths by 5 September; preliminary data</t>
+        </is>
+      </c>
+      <c r="U163" s="5" t="inlineStr">
+        <is>
+          <t>Approximate health-zone reference; epidemiological data require official validation</t>
+        </is>
+      </c>
+      <c r="V163" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/INRB-UMIE/BDBV2026-Data/blob/main/data/insp_sitrep/processed/insp_sitrep__cumulative_confirmed_cases__daily.csv</t>
+        </is>
+      </c>
+      <c r="W163" s="5" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="X163" s="5" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+      <c r="Y163" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="Z163" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AA163" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AB163" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="AC163" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response record; beneficiary estimate not calculated</t>
+        </is>
+      </c>
+      <c r="AD163" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable for response activity record</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>EB-2026-005</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>INSP / DRC public health response</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>Government / public health</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Community engagement</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>Community communication around confirmed Wamba cases</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>Improve risk awareness and promote timely care-seeking and prevention</t>
+        </is>
+      </c>
+      <c r="G164" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="H164" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I164" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J164" s="5" t="inlineStr">
+        <is>
+          <t>Haut-Uele</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="inlineStr">
+        <is>
+          <t>Wamba</t>
+        </is>
+      </c>
+      <c r="L164" s="5" t="inlineStr">
+        <is>
+          <t>Wamba</t>
+        </is>
+      </c>
+      <c r="M164" s="5" t="inlineStr">
+        <is>
+          <t>Wamba Health Zone</t>
+        </is>
+      </c>
+      <c r="N164" s="5" t="inlineStr">
+        <is>
+          <t>2.14° N, 27.99° E</t>
+        </is>
+      </c>
+      <c r="O164" s="5" t="inlineStr">
+        <is>
+          <t>3,705 people reached</t>
+        </is>
+      </c>
+      <c r="P164" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q164" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="R164" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="S164" s="5" t="inlineStr">
+        <is>
+          <t>Current preliminary</t>
+        </is>
+      </c>
+      <c r="T164" s="5" t="inlineStr">
+        <is>
+          <t>National INSP sitrep records community communication reaching 3,705 people in Wamba; implementing partner not specified</t>
+        </is>
+      </c>
+      <c r="U164" s="5" t="inlineStr">
+        <is>
+          <t>Approximate health-zone reference; reach figure is not a unique beneficiary count</t>
+        </is>
+      </c>
+      <c r="V164" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/INRB-UMIE/BDBV2026-Data/blob/main/data/public_health_response/processed/public_health_response__national_epidemiological_community_engagement_en__daily.csv</t>
+        </is>
+      </c>
+      <c r="W164" s="5" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="X164" s="5" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+      <c r="Y164" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="Z164" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AA164" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="AB164" s="5" t="inlineStr">
+        <is>
+          <t>Not calculated</t>
+        </is>
+      </c>
+      <c r="AC164" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response record; beneficiary estimate not calculated</t>
+        </is>
+      </c>
+      <c r="AD164" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable for response activity record</t>
         </is>
       </c>
     </row>
@@ -45042,7 +46621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V154"/>
+  <dimension ref="A1:V164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -60122,6 +61701,1126 @@
       <c r="V154" s="9" t="inlineStr">
         <is>
           <t>HDX/OCHA DRC Subnational Population Statistics 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>EB-2019-001</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF Ebola Emergency Operations Centre</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>UN agency</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Surveillance</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>Ebola case surveillance and line-list reporting in Mandima Health Zone</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>2018-2019</t>
+        </is>
+      </c>
+      <c r="G155" s="5" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="I155" s="5" t="inlineStr">
+        <is>
+          <t>Mandima</t>
+        </is>
+      </c>
+      <c r="J155" s="5" t="inlineStr">
+        <is>
+          <t>Mandima Health Zone</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="inlineStr">
+        <is>
+          <t>0.87° N, 29.75° E</t>
+        </is>
+      </c>
+      <c r="L155" s="12" t="inlineStr">
+        <is>
+          <t>Historical verified</t>
+        </is>
+      </c>
+      <c r="M155" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF EOC annual dashboard: 238 Mandima line-list records (234 confirmed, 4 probable); health-zone geography used as Mambasa Territory proxy</t>
+        </is>
+      </c>
+      <c r="N155" s="10" t="inlineStr">
+        <is>
+          <t>2018-08-05</t>
+        </is>
+      </c>
+      <c r="O155" s="10" t="inlineStr">
+        <is>
+          <t>2019-08-05</t>
+        </is>
+      </c>
+      <c r="P155" s="5" t="inlineStr">
+        <is>
+          <t>2018-2019</t>
+        </is>
+      </c>
+      <c r="Q155" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response evidence: UNICEF EOC / INSP-INRB BDBV</t>
+        </is>
+      </c>
+      <c r="R155" s="5" t="inlineStr">
+        <is>
+          <t>https://data.humdata.org/dataset/a3fe7795-dbe3-410f-942c-ef407c040868/resource/deaa1018-df33-4b92-8afc-c67f0b2c0fea/download/annual-dashboard-unicef-eoc.xlsx</t>
+        </is>
+      </c>
+      <c r="S155" s="5" t="inlineStr">
+        <is>
+          <t>Approximate health-zone reference; territory assignment requires validation</t>
+        </is>
+      </c>
+      <c r="T155" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF EOC annual dashboard: 238 Mandima line-list records (234 confirmed, 4 probable); health-zone geography used as Mambasa Territory proxy</t>
+        </is>
+      </c>
+      <c r="U155" s="9" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="V155" s="9" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>EB-2019-002</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF Ebola Emergency Operations Centre</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>UN agency</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Surveillance</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>Ebola case investigation and line-list reporting in Mambasa Health Zone</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="G156" s="5" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="I156" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="J156" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa Health Zone</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="inlineStr">
+        <is>
+          <t>1.55° N, 27.20° E</t>
+        </is>
+      </c>
+      <c r="L156" s="12" t="inlineStr">
+        <is>
+          <t>Historical verified</t>
+        </is>
+      </c>
+      <c r="M156" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF EOC annual dashboard records 9 confirmed Mambasa-zone cases; health-zone geography used as territory proxy</t>
+        </is>
+      </c>
+      <c r="N156" s="10" t="inlineStr">
+        <is>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="O156" s="10" t="inlineStr">
+        <is>
+          <t>2019-08-05</t>
+        </is>
+      </c>
+      <c r="P156" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q156" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response evidence: UNICEF EOC / INSP-INRB BDBV</t>
+        </is>
+      </c>
+      <c r="R156" s="5" t="inlineStr">
+        <is>
+          <t>https://data.humdata.org/dataset/a3fe7795-dbe3-410f-942c-ef407c040868/resource/deaa1018-df33-4b92-8afc-c67f0b2c0fea/download/annual-dashboard-unicef-eoc.xlsx</t>
+        </is>
+      </c>
+      <c r="S156" s="5" t="inlineStr">
+        <is>
+          <t>Approximate health-zone reference; case counts are not beneficiary counts</t>
+        </is>
+      </c>
+      <c r="T156" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF EOC annual dashboard records 9 confirmed Mambasa-zone cases; health-zone geography used as territory proxy</t>
+        </is>
+      </c>
+      <c r="U156" s="9" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="V156" s="9" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>EB-2019-003</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF Ebola Emergency Operations Centre</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>UN agency</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Psychosocial and protection</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>Psychosocial support, child protection and family support during Ebola response</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa / Mandima</t>
+        </is>
+      </c>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa and Mandima Health Zones</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="inlineStr">
+        <is>
+          <t>1.21° N, 28.48° E</t>
+        </is>
+      </c>
+      <c r="L157" s="12" t="inlineStr">
+        <is>
+          <t>Historical verified</t>
+        </is>
+      </c>
+      <c r="M157" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF April 2019 psychosocial pillar database records CTE/CT support, psychoeducation and family assistance in both health zones</t>
+        </is>
+      </c>
+      <c r="N157" s="10" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="O157" s="10" t="inlineStr">
+        <is>
+          <t>2019-04-30</t>
+        </is>
+      </c>
+      <c r="P157" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q157" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response evidence: UNICEF EOC / INSP-INRB BDBV</t>
+        </is>
+      </c>
+      <c r="R157" s="5" t="inlineStr">
+        <is>
+          <t>https://data.humdata.org/dataset/b554c216-ab2e-4065-bc17-918f215bea86/resource/e4825dff-2410-4cfe-bb42-4a2b1d43ca02/download/psychosocial-avril-2019-unicef-eoc.xls</t>
+        </is>
+      </c>
+      <c r="S157" s="5" t="inlineStr">
+        <is>
+          <t>Approximate combined health-zone reference; validate locality-specific coverage</t>
+        </is>
+      </c>
+      <c r="T157" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF April 2019 psychosocial pillar database records CTE/CT support, psychoeducation and family assistance in both health zones</t>
+        </is>
+      </c>
+      <c r="U157" s="9" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="V157" s="9" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>EB-2019-004</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF Ebola Emergency Operations Centre</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>UN agency</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Psychosocial, protection and nutrition</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>Psychosocial support, separated-child assistance and nutrition support</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="I158" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa / Mandima</t>
+        </is>
+      </c>
+      <c r="J158" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa and Mandima Health Zones</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="inlineStr">
+        <is>
+          <t>1.21° N, 28.48° E</t>
+        </is>
+      </c>
+      <c r="L158" s="12" t="inlineStr">
+        <is>
+          <t>Historical verified</t>
+        </is>
+      </c>
+      <c r="M158" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF May 2019 psychosocial database records CTE support, contact/family follow-up and food/nutrition kit distribution in both zones</t>
+        </is>
+      </c>
+      <c r="N158" s="10" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="O158" s="10" t="inlineStr">
+        <is>
+          <t>2019-05-31</t>
+        </is>
+      </c>
+      <c r="P158" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q158" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response evidence: UNICEF EOC / INSP-INRB BDBV</t>
+        </is>
+      </c>
+      <c r="R158" s="5" t="inlineStr">
+        <is>
+          <t>https://data.humdata.org/dataset/d047e4be-091f-4afb-b677-c964262a3cc3/resource/0716d640-20b3-4ff7-a3cb-3eea0cb5a933/download/unicef-ebola-master_psychosocial_mai-2019.xls</t>
+        </is>
+      </c>
+      <c r="S158" s="5" t="inlineStr">
+        <is>
+          <t>Approximate combined health-zone reference; validate locality-specific coverage</t>
+        </is>
+      </c>
+      <c r="T158" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF May 2019 psychosocial database records CTE support, contact/family follow-up and food/nutrition kit distribution in both zones</t>
+        </is>
+      </c>
+      <c r="U158" s="9" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="V158" s="9" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>EB-2019-005</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF Ebola Emergency Operations Centre</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>UN agency</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Psychosocial and protection</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>Psychosocial support, contact/family follow-up and child protection</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa / Mandima</t>
+        </is>
+      </c>
+      <c r="J159" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa and Mandima Health Zones</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="inlineStr">
+        <is>
+          <t>1.21° N, 28.48° E</t>
+        </is>
+      </c>
+      <c r="L159" s="12" t="inlineStr">
+        <is>
+          <t>Historical verified</t>
+        </is>
+      </c>
+      <c r="M159" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF June 2019 psychosocial database records support for suspected/confirmed cases, contacts, families and children</t>
+        </is>
+      </c>
+      <c r="N159" s="10" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="O159" s="10" t="inlineStr">
+        <is>
+          <t>2019-06-30</t>
+        </is>
+      </c>
+      <c r="P159" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q159" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response evidence: UNICEF EOC / INSP-INRB BDBV</t>
+        </is>
+      </c>
+      <c r="R159" s="5" t="inlineStr">
+        <is>
+          <t>https://data.humdata.org/dataset/ec6827e1-e83b-4854-852e-a7c710f1685f/resource/81b3d06a-907d-4ed1-bb70-b02bd709cb64/download/unicef-ebola-master_psychosocial_juin-2019.xls</t>
+        </is>
+      </c>
+      <c r="S159" s="5" t="inlineStr">
+        <is>
+          <t>Approximate combined health-zone reference; validate locality-specific coverage</t>
+        </is>
+      </c>
+      <c r="T159" s="5" t="inlineStr">
+        <is>
+          <t>UNICEF June 2019 psychosocial database records support for suspected/confirmed cases, contacts, families and children</t>
+        </is>
+      </c>
+      <c r="U159" s="9" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="V159" s="9" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>EB-2026-001</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>INSP / INRB BDBV response</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>Government / public health</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Surveillance</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>Routine surveillance, alerts, investigations, active case finding and contact follow-up</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="J160" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa Health Zone</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="inlineStr">
+        <is>
+          <t>1.55° N, 27.20° E</t>
+        </is>
+      </c>
+      <c r="L160" s="12" t="inlineStr">
+        <is>
+          <t>Current preliminary</t>
+        </is>
+      </c>
+      <c r="M160" s="5" t="inlineStr">
+        <is>
+          <t>INSP/INRB public response monitoring records surveillance and investigations in Mambasa; preliminary sitrep-derived data</t>
+        </is>
+      </c>
+      <c r="N160" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="O160" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="P160" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q160" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response evidence: UNICEF EOC / INSP-INRB BDBV</t>
+        </is>
+      </c>
+      <c r="R160" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/INRB-UMIE/BDBV2026-Data</t>
+        </is>
+      </c>
+      <c r="S160" s="5" t="inlineStr">
+        <is>
+          <t>Approximate health-zone reference; BDBV records require routine official validation</t>
+        </is>
+      </c>
+      <c r="T160" s="5" t="inlineStr">
+        <is>
+          <t>INSP/INRB public response monitoring records surveillance and investigations in Mambasa; preliminary sitrep-derived data</t>
+        </is>
+      </c>
+      <c r="U160" s="9" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="V160" s="9" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>EB-2026-002</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>INSP / INRB BDBV response</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>Government / public health</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Infection prevention and control</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>IPC briefings, WASH and IPC kit distribution for Mambasa providers</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="I161" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="J161" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa Health Zone</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="inlineStr">
+        <is>
+          <t>1.55° N, 27.20° E</t>
+        </is>
+      </c>
+      <c r="L161" s="12" t="inlineStr">
+        <is>
+          <t>Current preliminary</t>
+        </is>
+      </c>
+      <c r="M161" s="5" t="inlineStr">
+        <is>
+          <t>INSP/INRB public response monitoring records provider briefings and IPC/WASH kit support in Mambasa</t>
+        </is>
+      </c>
+      <c r="N161" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="O161" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="P161" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q161" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response evidence: UNICEF EOC / INSP-INRB BDBV</t>
+        </is>
+      </c>
+      <c r="R161" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/INRB-UMIE/BDBV2026-Data</t>
+        </is>
+      </c>
+      <c r="S161" s="5" t="inlineStr">
+        <is>
+          <t>Approximate health-zone reference; BDBV records are preliminary</t>
+        </is>
+      </c>
+      <c r="T161" s="5" t="inlineStr">
+        <is>
+          <t>INSP/INRB public response monitoring records provider briefings and IPC/WASH kit support in Mambasa</t>
+        </is>
+      </c>
+      <c r="U161" s="9" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="V161" s="9" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>EB-2026-003</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>INSP / INRB BDBV response</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>Government / public health</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Points of control and laboratory preparedness</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>Activation of points of control, referrals and laboratory preparedness</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="I162" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="J162" s="5" t="inlineStr">
+        <is>
+          <t>Mabake / Mambasa points of control and Mambasa Health Zone</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="inlineStr">
+        <is>
+          <t>1.55° N, 27.20° E</t>
+        </is>
+      </c>
+      <c r="L162" s="12" t="inlineStr">
+        <is>
+          <t>Current preliminary</t>
+        </is>
+      </c>
+      <c r="M162" s="5" t="inlineStr">
+        <is>
+          <t>INSP/INRB provincial monitoring records PoC activation, referrals and laboratory installations; WHO-supported supplies are noted in logistics records</t>
+        </is>
+      </c>
+      <c r="N162" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="O162" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="P162" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q162" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response evidence: UNICEF EOC / INSP-INRB BDBV</t>
+        </is>
+      </c>
+      <c r="R162" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/INRB-UMIE/BDBV2026-Data</t>
+        </is>
+      </c>
+      <c r="S162" s="5" t="inlineStr">
+        <is>
+          <t>Approximate operational reference; names and boundaries require partner validation</t>
+        </is>
+      </c>
+      <c r="T162" s="5" t="inlineStr">
+        <is>
+          <t>INSP/INRB provincial monitoring records PoC activation, referrals and laboratory installations; WHO-supported supplies are noted in logistics records</t>
+        </is>
+      </c>
+      <c r="U162" s="9" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="V162" s="9" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>EB-2026-004</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>INSP / DRC public health response</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>Government / public health</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Surveillance</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>BDBV case surveillance and cumulative case/death monitoring</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>Haut-Uele</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>Wamba</t>
+        </is>
+      </c>
+      <c r="I163" s="5" t="inlineStr">
+        <is>
+          <t>Wamba</t>
+        </is>
+      </c>
+      <c r="J163" s="5" t="inlineStr">
+        <is>
+          <t>Wamba Health Zone</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="inlineStr">
+        <is>
+          <t>2.14° N, 27.99° E</t>
+        </is>
+      </c>
+      <c r="L163" s="12" t="inlineStr">
+        <is>
+          <t>Current preliminary</t>
+        </is>
+      </c>
+      <c r="M163" s="5" t="inlineStr">
+        <is>
+          <t>INSP/INRB-derived cumulative series reports Wamba first confirmed case on 10 July and 83 confirmed cases/31 deaths by 5 September; preliminary data</t>
+        </is>
+      </c>
+      <c r="N163" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="O163" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="P163" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q163" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response evidence: UNICEF EOC / INSP-INRB BDBV</t>
+        </is>
+      </c>
+      <c r="R163" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/INRB-UMIE/BDBV2026-Data</t>
+        </is>
+      </c>
+      <c r="S163" s="5" t="inlineStr">
+        <is>
+          <t>Approximate health-zone reference; epidemiological data require official validation</t>
+        </is>
+      </c>
+      <c r="T163" s="5" t="inlineStr">
+        <is>
+          <t>INSP/INRB-derived cumulative series reports Wamba first confirmed case on 10 July and 83 confirmed cases/31 deaths by 5 September; preliminary data</t>
+        </is>
+      </c>
+      <c r="U163" s="9" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="V163" s="9" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>EB-2026-005</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>INSP / DRC public health response</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>Government / public health</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response / Community engagement</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>Community communication around confirmed Wamba cases</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>Haut-Uele</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
+          <t>Wamba</t>
+        </is>
+      </c>
+      <c r="I164" s="5" t="inlineStr">
+        <is>
+          <t>Wamba</t>
+        </is>
+      </c>
+      <c r="J164" s="5" t="inlineStr">
+        <is>
+          <t>Wamba Health Zone</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="inlineStr">
+        <is>
+          <t>2.14° N, 27.99° E</t>
+        </is>
+      </c>
+      <c r="L164" s="12" t="inlineStr">
+        <is>
+          <t>Current preliminary</t>
+        </is>
+      </c>
+      <c r="M164" s="5" t="inlineStr">
+        <is>
+          <t>National INSP sitrep records community communication reaching 3,705 people in Wamba; implementing partner not specified</t>
+        </is>
+      </c>
+      <c r="N164" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="O164" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="P164" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q164" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response evidence: UNICEF EOC / INSP-INRB BDBV</t>
+        </is>
+      </c>
+      <c r="R164" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/INRB-UMIE/BDBV2026-Data</t>
+        </is>
+      </c>
+      <c r="S164" s="5" t="inlineStr">
+        <is>
+          <t>Approximate health-zone reference; reach figure is not a unique beneficiary count</t>
+        </is>
+      </c>
+      <c r="T164" s="5" t="inlineStr">
+        <is>
+          <t>National INSP sitrep records community communication reaching 3,705 people in Wamba; implementing partner not specified</t>
+        </is>
+      </c>
+      <c r="U164" s="9" t="inlineStr">
+        <is>
+          <t>See territory planning estimate</t>
+        </is>
+      </c>
+      <c r="V164" s="9" t="inlineStr">
+        <is>
+          <t>HDX/OCHA 2024; Ebola record is not a population estimate</t>
         </is>
       </c>
     </row>
@@ -61731,7 +64430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -62014,6 +64713,42 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ebola response records</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Verified historical UNICEF EOC records cover Mambasa and Mandima Health Zones during the 2018-2019 North Kivu/Ituri Ebola outbreak. Preliminary INSP/INRB BDBV monitoring records cover Mambasa in June-July 2026 and Wamba in July-September 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ebola geographic limitation</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Health zones are used as operational geography proxies for territory-level reporting. Watsa has no verified Ebola-specific operation in the reviewed public sources; this is an evidence gap, not proof of no activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ebola beneficiary limitation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ebola case counts, people reached and response outputs are not interchangeable with unique beneficiaries. They remain in source/verification fields and are not added to WorldPop intervention estimates.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RFO_Stakeholders Final.xlsx
+++ b/RFO_Stakeholders Final.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical Coverage" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3W Matrix (Who does What Where)" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cluster Summary (Who Does What)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ebola Organisations" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RFO_Stakeholders Final'!$A$1:$T$29</definedName>
@@ -29,6 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Coverage Summary'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Data Sources'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Historical Coverage'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Ebola Organisations'!$A$1:$I$11</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -59,7 +61,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -103,6 +105,11 @@
         <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000B1F33"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -141,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -192,6 +199,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -687,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y29"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3792,7 +3802,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Protection, WASH</t>
+          <t>Protection, WASH; Ebola response</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
@@ -3802,12 +3812,12 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026; 2018-2019; 2026</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>Biakato, Ibambi, Mambasa Centre, Pawa, Wamba Centre</t>
+          <t>Biakato, Ibambi, Mambasa Centre, Pawa, Wamba Centre; Mambasa, Mandima, Wamba</t>
         </is>
       </c>
       <c r="I26" s="5" t="n">
@@ -3860,12 +3870,12 @@
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>No budget total published; validate with partner</t>
+          <t>No budget total published; validate with partner; Ebola role source-backed; exact local outputs require validation</t>
         </is>
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>Mambasa Humanitarian workbook - à valider</t>
+          <t>Mambasa Humanitarian workbook - à valider; UNICEF EOC Ebola datasets; INSP/INRB BDBV2026 public data</t>
         </is>
       </c>
       <c r="U26" s="9" t="n">
@@ -4260,6 +4270,93 @@
           <t>Planning population estimate, not beneficiary count or census</t>
         </is>
       </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>INSP / INRB</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Government / public health institute</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Ituri; Haut-Uele</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa; Wamba</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Ebola response: surveillance, IPC/WASH, points of control, laboratory preparedness, community engagement</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>Detect and contain Bundibugyo virus transmission and maintain public-health readiness</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Mambasa Health Zone; Wamba Health Zone</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>10 Ebola response records</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Approximate health-zone references</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>Mambasa 1.55° N, 27.20° E; Wamba 2.14° N, 27.99° E</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>Health-zone proxy; validate exact operational sites</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>Response outputs and case data are not unique beneficiary counts</t>
+        </is>
+      </c>
+      <c r="P30" s="5" t="n"/>
+      <c r="Q30" s="5" t="n"/>
+      <c r="R30" s="5" t="n"/>
+      <c r="S30" s="5" t="inlineStr">
+        <is>
+          <t>Preliminary public INSP/INRB data; validate with response coordination</t>
+        </is>
+      </c>
+      <c r="T30" s="5" t="inlineStr">
+        <is>
+          <t>INSP/INRB BDBV2026 public data</t>
+        </is>
+      </c>
+      <c r="U30" s="9" t="n"/>
+      <c r="V30" s="9" t="n"/>
+      <c r="W30" s="9" t="n"/>
+      <c r="X30" s="9" t="n"/>
+      <c r="Y30" s="9" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:T29"/>
@@ -7948,6 +8045,549 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="72" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>Actor Type</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>Province(s)</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>Territory(ies)</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>Ebola response role / sector</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>Operation years</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
+          <t>Evidence and geographic note</t>
+        </is>
+      </c>
+      <c r="H1" s="18" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="I1" s="18" t="inlineStr">
+        <is>
+          <t>Verification status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>INSP / INRB</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Government / public health institute</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>Ituri; Haut-Uele</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Mambasa; Wamba</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Surveillance, IPC/WASH, points of control, laboratory preparedness, community engagement</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>Mambasa and Wamba records are preliminary BDBV monitoring data; verify with official response coordination</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/INRB-UMIE/BDBV2026-Data</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>Verified public-source response actor; preliminary data</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>UNICEF Ebola Emergency Operations Centre</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>UN agency / response coordination</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Surveillance, psychosocial support, child protection, nutrition and family support</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>2018-2019</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>UNICEF EOC dashboards and psychosocial pillar datasets document Mambasa and Mandima health-zone activities</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>https://data.humdata.org/dataset/unicef-eoc-2018-2019-dashboard-en-final</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Verified public-source response actor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>DRC Ministry of Health</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Government / public health</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Ituri; Haut-Uele</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Mambasa; Wamba</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Ebola/BDBV response leadership, surveillance, case management and coordination</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>2018-2019; 2026</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Named as the national response authority in UNICEF, CDC and INSP/INRB public response sources; territory-level implementing detail requires validation</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/mmwr/volumes/68/wr/mm6850a3.htm</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Response authority; territory-level activity requires validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>WHO</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>UN agency / technical partner</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Ituri; Haut-Uele</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Mambasa; Wamba</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Technical support, emergency mapping, IPC, logistics and response coordination</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>2018-2019; 2026</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>WHO is identified in Ebola response sources and WHO-supported 2026 logistics records; exact organisation-level outputs require validation</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>https://data.humdata.org/dataset/drc-health-facilities</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Provincial/national response partner; local outputs require validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>OCHA</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>UN agency / coordination</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Ituri; Haut-Uele</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Mambasa; Wamba</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Humanitarian coordination and response information management</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>2018-2019</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>CDC response context identifies OCHA among response partners; no locality-specific activity count asserted</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/mmwr/volumes/68/wr/mm6850a3.htm</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Provincial/national response partner; local outputs require validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>IOM</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>UN agency / humanitarian partner</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Humanitarian coordination, displacement and response support</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>2018-2019</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>CDC response context identifies IOM among response partners; no locality-specific activity count asserted</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/mmwr/volumes/68/wr/mm6850a3.htm</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Provincial/national response partner; local outputs require validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>ALIMA</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>International NGO / medical response partner</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Case management, treatment and emergency medical response</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>2018-2019</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>CDC response context identifies ALIMA among response partners; exact Mambasa activity requires partner validation</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/mmwr/volumes/68/wr/mm6850a3.htm</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Provincial/national response partner; local outputs require validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Médecins Sans Frontières (MSF)</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>International NGO / medical response partner</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Ituri; Haut-Uele</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Mambasa; Wamba</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Case management, IPC and emergency health response</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>2018-2019; 2026</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>MSF is an existing stakeholder and is named in CDC response context; Ebola-specific local outputs require validation</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/mmwr/volumes/68/wr/mm6850a3.htm</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Existing stakeholder; Ebola role requires local validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Croix-Rouge de la RDC</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>National NGO / response partner</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Ituri; Haut-Uele</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Mambasa; Wamba</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Community engagement, surveillance and emergency response support</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>2018-2019; 2026</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Existing stakeholder named in CDC response context; Ebola-specific local outputs require validation</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/mmwr/volumes/68/wr/mm6850a3.htm</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Existing stakeholder; Ebola role requires local validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>CDC</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Government technical partner</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Mambasa</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Technical assistance, surveillance and outbreak response support</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>2018-2019</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>CDC published response context for the North Kivu/Ituri Ebola outbreak; no locality-specific activity count asserted</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/mmwr/volumes/68/wr/mm6850a3.htm</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Technical response partner; local outputs require validation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/RFO_Stakeholders Final.xlsx
+++ b/RFO_Stakeholders Final.xlsx
@@ -20,6 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3W Matrix (Who does What Where)" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cluster Summary (Who Does What)" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ebola Organisations" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ebola Funding" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RFO_Stakeholders Final'!$A$1:$T$29</definedName>
@@ -31,6 +32,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Data Sources'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Historical Coverage'!$A$1:$E$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Ebola Organisations'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Ebola Funding'!$A$1:$K$11</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -8055,7 +8057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8115,6 +8117,21 @@
           <t>Verification status</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Funding source(s) / published amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Funding geographic scope</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Funding QA</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
@@ -8162,6 +8179,21 @@
           <t>Verified public-source response actor; preliminary data</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Not publicly published</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Mambasa/Wamba local funding not published</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>No public donor or amount identified</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -8209,6 +8241,21 @@
           <t>Verified public-source response actor</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CERF US$3,935,937; ECHO US$889,878 (2019)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>North Kivu and Ituri; not disaggregated to Mambasa/Mandima</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Source-backed provincial funding; local attribution unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -8256,6 +8303,21 @@
           <t>Response authority; territory-level activity requires validation</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Not separately published</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>National/provincial response authority</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>No ministry-specific amount identified</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -8303,6 +8365,21 @@
           <t>Provincial/national response partner; local outputs require validation</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CERF US$1,701,255 (2018); CERF US$3,902,590 (2019); ECHO US$8,476,085; Germany US$7,786,429</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>North Kivu and Ituri; not disaggregated to Mambasa/Mandima</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Source-backed provincial funding; local attribution unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -8350,6 +8427,21 @@
           <t>Provincial/national response partner; local outputs require validation</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Not separately published</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Response-wide/provincial context only</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>No organisation-specific amount identified</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -8397,6 +8489,21 @@
           <t>Provincial/national response partner; local outputs require validation</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CERF US$1,999,062 (2019)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>North Kivu and Ituri; not disaggregated to Mambasa/Mandima</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Source-backed provincial funding; local attribution unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -8444,6 +8551,21 @@
           <t>Provincial/national response partner; local outputs require validation</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Not separately published in reviewed FTS records</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Provincial response context only</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>No organisation-specific amount identified</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -8491,6 +8613,21 @@
           <t>Existing stakeholder; Ebola role requires local validation</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Not separately published in reviewed FTS records</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Provincial response context only</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>No organisation-specific amount identified</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -8538,6 +8675,21 @@
           <t>Existing stakeholder; Ebola role requires local validation</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Not separately published in reviewed FTS records</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Provincial response context only</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>No organisation-specific amount identified</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -8585,9 +8737,679 @@
           <t>Technical response partner; local outputs require validation</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Not separately published in reviewed FTS records</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Provincial response context only</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>No organisation-specific amount identified</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="56" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Funding ID</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>Operation year</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>Funder</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>Recipient / organisation</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>Published amount</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>Currency / amount basis</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
+          <t>Funding mechanism / status</t>
+        </is>
+      </c>
+      <c r="H1" s="18" t="inlineStr">
+        <is>
+          <t>Geographic scope</t>
+        </is>
+      </c>
+      <c r="I1" s="18" t="inlineStr">
+        <is>
+          <t>Funding date</t>
+        </is>
+      </c>
+      <c r="J1" s="18" t="inlineStr">
+        <is>
+          <t>Funding QA / local attribution</t>
+        </is>
+      </c>
+      <c r="K1" s="18" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>FND-EB-2018-001</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>CERF</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>WHO</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>1,701,255</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>CERF pooled-fund allocation; paid; unearmarked</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>North Kivu and Ituri provinces; not disaggregated to Mambasa/Mandima</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>Source-backed provincial scope; local allocation unavailable</t>
+        </is>
+      </c>
+      <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>https://api.hpc.tools/v1/public/fts/flow?filterBy%5B0%5D=destinationEmergencyId%3A707&amp;filterBy%5B1%5D=sourceOrganizationId%3A4762&amp;year=2018&amp;boundary=internal&amp;report=4&amp;format=json&amp;limit=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>FND-EB-2019-001</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>CERF</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>WHO</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>3,902,590</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>CERF pooled-fund allocation; paid; unearmarked</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>North Kivu and Ituri provinces; not disaggregated to Mambasa/Mandima</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>Source-backed provincial scope; local allocation unavailable</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>https://api.hpc.tools/v1/public/fts/flow?filterBy%5B0%5D=destinationEmergencyId%3A707&amp;filterBy%5B1%5D=sourceOrganizationId%3A4762&amp;year=2019&amp;boundary=internal&amp;report=4&amp;format=json&amp;limit=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>FND-EB-2019-002</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>CERF</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>IOM</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>1,999,062</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>CERF pooled-fund allocation; paid; unearmarked</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>North Kivu and Ituri provinces; not disaggregated to Mambasa/Mandima</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>Source-backed provincial scope; local allocation unavailable</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>https://api.hpc.tools/v1/public/fts/flow?filterBy%5B0%5D=destinationEmergencyId%3A707&amp;filterBy%5B1%5D=sourceOrganizationId%3A4762&amp;year=2019&amp;boundary=internal&amp;report=4&amp;format=json&amp;limit=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>FND-EB-2019-003</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>CERF</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>UNICEF</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>3,935,937</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>CERF pooled-fund allocation; paid; unearmarked</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>North Kivu and Ituri provinces; not disaggregated to Mambasa/Mandima</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>2019-09-16</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Source-backed provincial scope; local allocation unavailable</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>https://api.hpc.tools/v1/public/fts/flow?filterBy%5B0%5D=destinationEmergencyId%3A707&amp;filterBy%5B1%5D=sourceOrganizationId%3A4762&amp;year=2019&amp;boundary=internal&amp;report=4&amp;format=json&amp;limit=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>FND-EB-2019-004</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>European Commission Humanitarian Aid and Civil Protection (ECHO)</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>WHO</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>8,476,085</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>USD (original EUR 7,620,000)</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>ECHO grant; earmarked; commitment; ref. ECHO/COD/BUD/2019/91025</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>North Kivu and Ituri provinces; not disaggregated to Mambasa/Mandima</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>2019-07-04</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>Source-backed provincial scope; local allocation unavailable</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>https://api.hpc.tools/v1/public/fts/flow?filterBy%5B0%5D=destinationEmergencyId%3A707&amp;filterBy%5B1%5D=sourceOrganizationId%3A8523&amp;filterBy%5B2%5D=destinationOrganizationId%3A4398&amp;year=2019&amp;boundary=incoming&amp;report=4&amp;format=json&amp;limit=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>FND-EB-2019-005</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>WHO</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>7,786,429</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>USD (original EUR 7,000,000)</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Government grant; earmarked; commitment; ref. AA-S09 321.50 COD 04/19</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>North Kivu and Ituri; not disaggregated to Mambasa/Mandima</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>2019-06-05</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Source-backed provincial scope; local allocation unavailable</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>https://api.hpc.tools/v1/public/fts/flow?filterBy%5B0%5D=destinationEmergencyId%3A707&amp;filterBy%5B1%5D=sourceOrganizationId%3A4306&amp;filterBy%5B2%5D=destinationOrganizationId%3A4398&amp;year=2019&amp;boundary=incoming&amp;report=4&amp;format=json&amp;limit=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>FND-EB-2019-006</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>European Commission Humanitarian Aid and Civil Protection (ECHO)</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>UNICEF</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>889,878</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>USD (original EUR 800,000)</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>ECHO grant; earmarked; paid; ref. ECHO/COD/BUD/2019/91024</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>North Kivu and Ituri; not disaggregated to Mambasa/Mandima</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>2019-06-28</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>Source-backed provincial scope; local allocation unavailable</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>https://api.hpc.tools/v1/public/fts/flow?filterBy%5B0%5D=destinationEmergencyId%3A707&amp;filterBy%5B1%5D=sourceOrganizationId%3A8523&amp;filterBy%5B2%5D=destinationOrganizationId%3A2915&amp;year=2019&amp;boundary=incoming&amp;report=4&amp;format=json&amp;limit=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>FND-EB-2019-007</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Action Against Hunger / ACF</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>538,851</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>USD (original SEK 5,000,000)</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Government grant; earmarked; commitment</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Emergency response to spread of Ebola in Ituri; not disaggregated to Mambasa</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>2019-07-26</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>Source-backed Ituri scope; local allocation unavailable</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>https://api.hpc.tools/v1/public/fts/flow?filterBy%5B0%5D=destinationEmergencyId%3A707&amp;filterBy%5B1%5D=sourceOrganizationId%3A2921&amp;filterBy%5B2%5D=destinationOrganizationId%3A4536&amp;year=2019&amp;boundary=incoming&amp;report=4&amp;format=json&amp;limit=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>FND-EB-2019-008</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>European Commission Humanitarian Aid and Civil Protection (ECHO)</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Malteser International</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>888,889</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>USD (original EUR 800,000)</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>ECHO grant; earmarked; commitment; ref. ECHO/COD/BUD/2019/91032</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>Northeast Ituri and Haut-Uele; not disaggregated to Mambasa/Watsa/Wamba</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>2019-11-05</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>Source-backed regional scope; local allocation unavailable</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>https://api.hpc.tools/v1/public/fts/flow?filterBy%5B0%5D=destinationEmergencyId%3A707&amp;filterBy%5B1%5D=sourceOrganizationId%3A8523&amp;filterBy%5B2%5D=destinationOrganizationId%3A173&amp;year=2019&amp;boundary=incoming&amp;report=4&amp;format=json&amp;limit=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>FND-EB-2026-001</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>OCHA FTS</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>BDBV response</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>0 reported</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>No incoming, outgoing or internal transactions returned in the reviewed FTS query</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>DRC country emergency; no Mambasa/Wamba allocation published</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>Source-backed unavailable; zero reported flows do not prove no funding</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>https://api.hpc.tools/v2/public/emergency/id/1031</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
